--- a/docs/0OMsoqOg9GiJ2xusVHMv/.gitbook/assets/IO - Template servizi - Locazione locali e impianti comunali (1).xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHMv/.gitbook/assets/IO - Template servizi - Locazione locali e impianti comunali (1).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="123">
   <si>
     <r>
       <t xml:space="preserve">
@@ -796,8 +796,8 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
-Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
+Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Se hai già provveduto a pagare l'avviso ignora questo messaggio.
 Se vuoi hai tempo fino al </t>
     </r>
     <r>
@@ -1488,9 +1488,6 @@
   </si>
   <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
     <t>Vedi Avviso</t>
@@ -2418,18 +2415,18 @@
         <v>97</v>
       </c>
       <c r="K6" s="34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L6" s="34" t="s">
         <v>97</v>
       </c>
       <c r="M6" s="34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>62</v>
@@ -2470,7 +2467,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>97</v>
@@ -2511,89 +2508,89 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="C9" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="F9" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="D9" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9" s="34" t="s">
+      <c r="G9" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="F9" s="34" t="s">
+      <c r="H9" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="I9" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="J9" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="H9" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="J9" s="34" t="s">
+      <c r="K9" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="K9" s="34" t="s">
+      <c r="L9" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="L9" s="34" t="s">
+      <c r="M9" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="M9" s="34" t="s">
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="B10" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="C10" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="D10" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="E10" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="F10" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="G10" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="J10" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="G10" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="I10" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="J10" s="34" t="s">
+      <c r="K10" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="K10" s="34" t="s">
+      <c r="L10" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="L10" s="34" t="s">
+      <c r="M10" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="M10" s="34" t="s">
-        <v>120</v>
-      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>62</v>
@@ -2605,10 +2602,10 @@
         <v>62</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G11" s="34" t="s">
         <v>62</v>
